--- a/artfynd/A 32908-2023 artfynd.xlsx
+++ b/artfynd/A 32908-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131791</v>
+        <v>122131784</v>
       </c>
       <c r="B2" t="n">
-        <v>78632</v>
+        <v>91040</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569765</v>
+        <v>569773</v>
       </c>
       <c r="R2" t="n">
-        <v>7108215</v>
+        <v>7108198</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131790</v>
+        <v>122131744</v>
       </c>
       <c r="B3" t="n">
-        <v>78632</v>
+        <v>97103</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Illvädersmyran, Ång</t>
+          <t>Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569787</v>
+        <v>570305</v>
       </c>
       <c r="R3" t="n">
-        <v>7108197</v>
+        <v>7108283</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131744</v>
+        <v>122131790</v>
       </c>
       <c r="B4" t="n">
-        <v>97094</v>
+        <v>78639</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergmyran, Ång</t>
+          <t>Illvädersmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570305</v>
+        <v>569787</v>
       </c>
       <c r="R4" t="n">
-        <v>7108283</v>
+        <v>7108197</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131784</v>
+        <v>122131791</v>
       </c>
       <c r="B5" t="n">
-        <v>91031</v>
+        <v>78639</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569773</v>
+        <v>569765</v>
       </c>
       <c r="R5" t="n">
-        <v>7108198</v>
+        <v>7108215</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 32908-2023 artfynd.xlsx
+++ b/artfynd/A 32908-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131790</v>
+        <v>122131744</v>
       </c>
       <c r="B2" t="n">
-        <v>78645</v>
+        <v>97129</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Illvädersmyran, Ång</t>
+          <t>Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569787</v>
+        <v>570305</v>
       </c>
       <c r="R2" t="n">
-        <v>7108197</v>
+        <v>7108283</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131744</v>
+        <v>122131791</v>
       </c>
       <c r="B3" t="n">
-        <v>97129</v>
+        <v>78645</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergmyran, Ång</t>
+          <t>Illvädersmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570305</v>
+        <v>569765</v>
       </c>
       <c r="R3" t="n">
-        <v>7108283</v>
+        <v>7108215</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131791</v>
+        <v>122131784</v>
       </c>
       <c r="B4" t="n">
-        <v>78645</v>
+        <v>91065</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569765</v>
+        <v>569773</v>
       </c>
       <c r="R4" t="n">
-        <v>7108215</v>
+        <v>7108198</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131784</v>
+        <v>122131790</v>
       </c>
       <c r="B5" t="n">
-        <v>91065</v>
+        <v>78645</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569773</v>
+        <v>569787</v>
       </c>
       <c r="R5" t="n">
-        <v>7108198</v>
+        <v>7108197</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 32908-2023 artfynd.xlsx
+++ b/artfynd/A 32908-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131744</v>
+        <v>122131791</v>
       </c>
       <c r="B2" t="n">
-        <v>97129</v>
+        <v>78646</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergmyran, Ång</t>
+          <t>Illvädersmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570305</v>
+        <v>569765</v>
       </c>
       <c r="R2" t="n">
-        <v>7108283</v>
+        <v>7108215</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131791</v>
+        <v>122131784</v>
       </c>
       <c r="B3" t="n">
-        <v>78645</v>
+        <v>91075</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569765</v>
+        <v>569773</v>
       </c>
       <c r="R3" t="n">
-        <v>7108215</v>
+        <v>7108198</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131784</v>
+        <v>122131744</v>
       </c>
       <c r="B4" t="n">
-        <v>91065</v>
+        <v>97139</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Illvädersmyran, Ång</t>
+          <t>Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569773</v>
+        <v>570305</v>
       </c>
       <c r="R4" t="n">
-        <v>7108198</v>
+        <v>7108283</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>122131790</v>
       </c>
       <c r="B5" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 32908-2023 artfynd.xlsx
+++ b/artfynd/A 32908-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131791</v>
+        <v>122131744</v>
       </c>
       <c r="B2" t="n">
-        <v>78646</v>
+        <v>97139</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Illvädersmyran, Ång</t>
+          <t>Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569765</v>
+        <v>570305</v>
       </c>
       <c r="R2" t="n">
-        <v>7108215</v>
+        <v>7108283</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131784</v>
+        <v>122131791</v>
       </c>
       <c r="B3" t="n">
-        <v>91075</v>
+        <v>78646</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569773</v>
+        <v>569765</v>
       </c>
       <c r="R3" t="n">
-        <v>7108198</v>
+        <v>7108215</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131744</v>
+        <v>122131790</v>
       </c>
       <c r="B4" t="n">
-        <v>97139</v>
+        <v>78646</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergmyran, Ång</t>
+          <t>Illvädersmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570305</v>
+        <v>569787</v>
       </c>
       <c r="R4" t="n">
-        <v>7108283</v>
+        <v>7108197</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131790</v>
+        <v>122131784</v>
       </c>
       <c r="B5" t="n">
-        <v>78646</v>
+        <v>91075</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569787</v>
+        <v>569773</v>
       </c>
       <c r="R5" t="n">
-        <v>7108197</v>
+        <v>7108198</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 32908-2023 artfynd.xlsx
+++ b/artfynd/A 32908-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122131744</v>
       </c>
       <c r="B2" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131791</v>
+        <v>122131784</v>
       </c>
       <c r="B3" t="n">
-        <v>78646</v>
+        <v>91087</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569765</v>
+        <v>569773</v>
       </c>
       <c r="R3" t="n">
-        <v>7108215</v>
+        <v>7108198</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>122131790</v>
       </c>
       <c r="B4" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131784</v>
+        <v>122131791</v>
       </c>
       <c r="B5" t="n">
-        <v>91075</v>
+        <v>78651</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569773</v>
+        <v>569765</v>
       </c>
       <c r="R5" t="n">
-        <v>7108198</v>
+        <v>7108215</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 32908-2023 artfynd.xlsx
+++ b/artfynd/A 32908-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131744</v>
+        <v>122131791</v>
       </c>
       <c r="B2" t="n">
-        <v>97151</v>
+        <v>78651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergmyran, Ång</t>
+          <t>Illvädersmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570305</v>
+        <v>569765</v>
       </c>
       <c r="R2" t="n">
-        <v>7108283</v>
+        <v>7108215</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +780,7 @@
         <v>122131784</v>
       </c>
       <c r="B3" t="n">
-        <v>91087</v>
+        <v>91092</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131791</v>
+        <v>122131744</v>
       </c>
       <c r="B5" t="n">
-        <v>78651</v>
+        <v>97156</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Illvädersmyran, Ång</t>
+          <t>Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569765</v>
+        <v>570305</v>
       </c>
       <c r="R5" t="n">
-        <v>7108215</v>
+        <v>7108283</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 32908-2023 artfynd.xlsx
+++ b/artfynd/A 32908-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131791</v>
+        <v>122131744</v>
       </c>
       <c r="B2" t="n">
-        <v>78651</v>
+        <v>97165</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Illvädersmyran, Ång</t>
+          <t>Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569765</v>
+        <v>570305</v>
       </c>
       <c r="R2" t="n">
-        <v>7108215</v>
+        <v>7108283</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +775,7 @@
         <v>122131784</v>
       </c>
       <c r="B3" t="n">
-        <v>91092</v>
+        <v>91097</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,11 +789,6 @@
       </c>
       <c r="E3" t="n">
         <v>658</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -882,7 +872,7 @@
         <v>122131790</v>
       </c>
       <c r="B4" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,11 +886,6 @@
       </c>
       <c r="E4" t="n">
         <v>6425</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -981,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131744</v>
+        <v>122131791</v>
       </c>
       <c r="B5" t="n">
-        <v>97156</v>
+        <v>78652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +978,33 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bergmyran, Ång</t>
+          <t>Illvädersmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570305</v>
+        <v>569765</v>
       </c>
       <c r="R5" t="n">
-        <v>7108283</v>
+        <v>7108215</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 32908-2023 artfynd.xlsx
+++ b/artfynd/A 32908-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131744</v>
+        <v>122131790</v>
       </c>
       <c r="B2" t="n">
-        <v>97165</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,33 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergmyran, Ång</t>
+          <t>Illvädersmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570305</v>
+        <v>569787</v>
       </c>
       <c r="R2" t="n">
-        <v>7108283</v>
+        <v>7108197</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131784</v>
+        <v>122131744</v>
       </c>
       <c r="B3" t="n">
-        <v>91097</v>
+        <v>97178</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -784,33 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>221945</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Illvädersmyran, Ång</t>
+          <t>Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569773</v>
+        <v>570305</v>
       </c>
       <c r="R3" t="n">
-        <v>7108198</v>
+        <v>7108283</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131790</v>
+        <v>122131791</v>
       </c>
       <c r="B4" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -887,6 +897,11 @@
       <c r="E4" t="n">
         <v>6425</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -904,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569787</v>
+        <v>569765</v>
       </c>
       <c r="R4" t="n">
-        <v>7108197</v>
+        <v>7108215</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131791</v>
+        <v>122131784</v>
       </c>
       <c r="B5" t="n">
-        <v>78652</v>
+        <v>91110</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -982,16 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>658</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569765</v>
+        <v>569773</v>
       </c>
       <c r="R5" t="n">
-        <v>7108215</v>
+        <v>7108198</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 32908-2023 artfynd.xlsx
+++ b/artfynd/A 32908-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131790</v>
+        <v>122131791</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569787</v>
+        <v>569765</v>
       </c>
       <c r="R2" t="n">
-        <v>7108197</v>
+        <v>7108215</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131744</v>
+        <v>122131790</v>
       </c>
       <c r="B3" t="n">
-        <v>97178</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergmyran, Ång</t>
+          <t>Illvädersmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570305</v>
+        <v>569787</v>
       </c>
       <c r="R3" t="n">
-        <v>7108283</v>
+        <v>7108197</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131791</v>
+        <v>122131784</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>91123</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569765</v>
+        <v>569773</v>
       </c>
       <c r="R4" t="n">
-        <v>7108215</v>
+        <v>7108198</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131784</v>
+        <v>122131744</v>
       </c>
       <c r="B5" t="n">
-        <v>91110</v>
+        <v>97191</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Illvädersmyran, Ång</t>
+          <t>Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569773</v>
+        <v>570305</v>
       </c>
       <c r="R5" t="n">
-        <v>7108198</v>
+        <v>7108283</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 32908-2023 artfynd.xlsx
+++ b/artfynd/A 32908-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131791</v>
+        <v>122131784</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569765</v>
+        <v>569773</v>
       </c>
       <c r="R2" t="n">
-        <v>7108215</v>
+        <v>7108198</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,16 +775,11 @@
         <v>122131790</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131784</v>
+        <v>122131791</v>
       </c>
       <c r="B4" t="n">
-        <v>91123</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569773</v>
+        <v>569765</v>
       </c>
       <c r="R4" t="n">
-        <v>7108198</v>
+        <v>7108215</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,12 +969,7 @@
         <v>122131744</v>
       </c>
       <c r="B5" t="n">
-        <v>97191</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,6 +1060,103 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122131759</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Illvädersmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>569726</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7108204</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bodum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32908-2023 artfynd.xlsx
+++ b/artfynd/A 32908-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122131784</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122131790</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122131791</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122131744</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,8 +1182,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122131759</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>